--- a/app/static/templates/领料单打印模板示例.xlsx
+++ b/app/static/templates/领料单打印模板示例.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="出库单模板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="领料单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,36 +37,15 @@
     <font>
       <name val="微软雅黑"/>
       <b val="1"/>
-      <color rgb="00FF0000"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <i val="1"/>
-      <color rgb="000000FF"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00FF0000"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -78,36 +57,38 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,275 +454,223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>出库单</t>
+          <t>领料单</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>单号：</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>{order.order_no}</t>
+          <t>领料部门：{order.customer}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>日期：{order.date}</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>日期：</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>{order.date}</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>物料编码</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>物料名称</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>合同编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>{item.material.code}</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>{item.material.brand}</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>{item.material.name}</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>{item.material.spec}</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>{item.material.unit.name}</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>{item.quantity}</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>{item.price}</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>{item.amount}</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>{item.contract_no}</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>客户/部门：{order.customer}</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>用途：{order.purpose}</t>
-        </is>
-      </c>
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>备注：{order.remark}</t>
-        </is>
-      </c>
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>物料编码</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>物料名称</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>规格</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>{item.material.code}</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>{item.material.name}</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>{item.material.spec}</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>{item.material.unit.name}</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>{item.quantity}</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>{item.price}</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>{item.amount}</t>
-        </is>
-      </c>
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>MAT-001</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>螺丝刀</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>十字，6mm</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>500</v>
-      </c>
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>MAT-002</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>开口，10mm</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>MAT-003</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>钳子</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>尖嘴</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>{total_quantity}</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>{total_amount}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>操作员：{order.operator.username}</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>打印时间：{print_date}</t>
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>领料：</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A13:D13"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G12:I12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
